--- a/diseases/d091/2005-2009.xlsx
+++ b/diseases/d091/2005-2009.xlsx
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN40" t="b">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -11769,7 +11769,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -13857,7 +13857,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -16789,7 +16789,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -17485,7 +17485,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -18181,7 +18181,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
